--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3A7ABB-0FC0-44C9-B805-C6CF73A19780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFA39F0-0B3D-4A05-BBA1-871DF395E102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -101,6 +101,102 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>Hero static template</t>
+  </si>
+  <si>
+    <t>Enemy static template</t>
+  </si>
+  <si>
+    <t>Initial deck static template</t>
+  </si>
+  <si>
+    <t>Card static template</t>
+  </si>
+  <si>
+    <t>Card effect static template</t>
+  </si>
+  <si>
+    <t>Battle encounter static template</t>
+  </si>
+  <si>
+    <t>battle.TbHero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.Hero</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.TbEnemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.Enemy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.TbDeck</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.Deck</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.TbCard</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.Card</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.TbCardEffect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.CardEffect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.TbEncounter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.Encounter</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.hero.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.enemy.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.deck.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.card_effect.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>battle.encounter.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -443,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -543,6 +639,144 @@
         <v>26</v>
       </c>
     </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -203,7 +203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,8 +224,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,6 +243,108 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F4FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF5F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F0F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7EFCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFE7F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5E9E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -256,11 +366,59 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -550,230 +708,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="6">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="7">
         <v>36</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" t="b" s="8">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="9">
         <v>47</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="10">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="11">
         <v>28</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="7">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="12">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="13">
         <v>38</v>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" t="b" s="14">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="15">
         <v>48</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="16">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="17">
         <v>28</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="13">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="6">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="7">
         <v>40</v>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" t="b" s="8">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="9">
         <v>49</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="10">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="11">
         <v>28</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="7">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="12">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="13">
         <v>42</v>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" t="b" s="14">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="15">
         <v>50</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="16">
         <v>27</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" t="s" s="17">
         <v>28</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" t="s" s="13">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="6">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" t="b" s="8">
         <v>1</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="9">
         <v>51</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="10">
         <v>27</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" t="s" s="11">
         <v>28</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" t="s" s="7">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="12">
         <v>45</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="13">
         <v>46</v>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" t="b" s="14">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="15">
         <v>52</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="16">
         <v>27</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" t="s" s="17">
         <v>28</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" t="s" s="13">
         <v>34</v>
       </c>
     </row>

--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re93b9bd0fa20493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R631dc41231ea4737"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -876,6 +876,31 @@
       <x:c r="J11"/>
       <x:c r="K11"/>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
+        <x:v>battle.TbCardUpgradeLevel</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>battle.CardUpgradeLevel</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>battle.card_upgrade_level.xlsx</x:v>
+      </x:c>
+      <x:c r="F12"/>
+      <x:c r="G12" t="str">
+        <x:v>list</x:v>
+      </x:c>
+      <x:c r="H12"/>
+      <x:c r="I12" t="str">
+        <x:v>Explicit finite card upgrade levels; runtime keys card_id + next_upgrade_level</x:v>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R631dc41231ea4737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6c2c309b2c14424d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -901,6 +901,60 @@
       <x:c r="J12"/>
       <x:c r="K12"/>
     </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
+        <x:v>run.TbRelic</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>run.Relic</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>run.relic.xlsx</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H13"/>
+      <x:c r="I13" t="str">
+        <x:v>Run relic static template</x:v>
+      </x:c>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
+        <x:v>run.TbPotion</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>run.Potion</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>run.potion.xlsx</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14" t="str">
+        <x:v>Run potion static template</x:v>
+      </x:c>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
